--- a/AAII_Financials/Yearly/BWIN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BWIN_YR_FIN.xlsx
@@ -2207,10 +2207,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>85800</v>
+        <v>806000</v>
       </c>
       <c r="E59" s="3">
-        <v>225300</v>
+        <v>866600</v>
       </c>
       <c r="F59" s="3">
         <v>306100</v>
